--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1001,8 +1001,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XER34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:XER39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1029,7 +1029,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1045,7 +1045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1061,7 +1061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1077,7 +1077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:16372">
+    <row r="6" customFormat="1" ht="14" spans="1:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1095,14 +1095,14 @@
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" spans="1:16372">
+    <row r="7" customFormat="1" ht="14" spans="1:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D34" si="0">E6+1</f>
+        <f t="shared" ref="D7:D39" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="2">
@@ -1114,7 +1114,7 @@
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" spans="1:16372">
+    <row r="8" customFormat="1" ht="14" spans="1:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1133,7 +1133,7 @@
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" spans="1:16372">
+    <row r="9" customFormat="1" ht="14" spans="1:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1152,7 +1152,7 @@
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" spans="1:16372">
+    <row r="10" customFormat="1" ht="14" spans="1:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1171,7 +1171,7 @@
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" spans="1:16372">
+    <row r="11" customFormat="1" ht="14" spans="1:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1190,7 +1190,7 @@
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" spans="1:16372">
+    <row r="12" customFormat="1" ht="14" spans="1:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -1209,7 +1209,7 @@
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" spans="1:16372">
+    <row r="13" customFormat="1" ht="14" spans="1:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -1228,7 +1228,7 @@
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" spans="1:16372">
+    <row r="14" customFormat="1" ht="14" spans="1:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -1247,7 +1247,7 @@
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" spans="1:16372">
+    <row r="15" customFormat="1" ht="14" spans="1:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
@@ -1266,7 +1266,7 @@
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" spans="1:16372">
+    <row r="16" customFormat="1" ht="14" spans="1:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -1285,7 +1285,7 @@
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" spans="1:16372">
+    <row r="17" customFormat="1" ht="14" spans="1:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2">
@@ -1304,7 +1304,7 @@
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" spans="1:16372">
+    <row r="18" customFormat="1" ht="14" spans="1:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
@@ -1323,7 +1323,7 @@
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" spans="1:16372">
+    <row r="19" customFormat="1" ht="14" spans="1:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2">
@@ -1342,7 +1342,7 @@
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" spans="1:16372">
+    <row r="20" customFormat="1" ht="14" spans="1:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2">
@@ -1361,7 +1361,7 @@
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" spans="1:16372">
+    <row r="21" customFormat="1" ht="14" spans="1:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2">
@@ -1380,7 +1380,7 @@
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" spans="1:16372">
+    <row r="22" customFormat="1" ht="14" spans="1:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2">
@@ -1399,7 +1399,7 @@
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" spans="1:16372">
+    <row r="23" customFormat="1" ht="14" spans="1:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2">
@@ -1418,7 +1418,7 @@
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" spans="1:16372">
+    <row r="24" customFormat="1" ht="14" spans="1:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
@@ -1437,7 +1437,7 @@
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" spans="1:16372">
+    <row r="25" customFormat="1" ht="14" spans="1:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2">
@@ -1456,7 +1456,7 @@
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" spans="1:16372">
+    <row r="26" customFormat="1" ht="14" spans="1:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2">
@@ -1475,7 +1475,7 @@
       <c r="XEQ26" s="2"/>
       <c r="XER26" s="2"/>
     </row>
-    <row r="27" spans="3:7">
+    <row r="27" ht="14" spans="3:7">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="3:7">
+    <row r="28" ht="14" spans="3:7">
       <c r="C28" s="2">
         <v>23</v>
       </c>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G28"/>
     </row>
-    <row r="29" spans="3:7">
+    <row r="29" ht="14" spans="3:7">
       <c r="C29" s="2">
         <v>24</v>
       </c>
@@ -1519,11 +1519,11 @@
         <v>95000</v>
       </c>
       <c r="F29" s="2">
-        <v>5750</v>
+        <v>5500</v>
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="3:7">
+    <row r="30" ht="14" spans="3:7">
       <c r="C30" s="2">
         <v>25</v>
       </c>
@@ -1535,11 +1535,11 @@
         <v>100000</v>
       </c>
       <c r="F30" s="2">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="3:7">
+    <row r="31" ht="14" spans="3:7">
       <c r="C31" s="2">
         <v>26</v>
       </c>
@@ -1551,11 +1551,11 @@
         <v>110000</v>
       </c>
       <c r="F31" s="2">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G31"/>
     </row>
-    <row r="32" spans="3:7">
+    <row r="32" ht="14" spans="3:7">
       <c r="C32" s="2">
         <v>27</v>
       </c>
@@ -1567,11 +1567,11 @@
         <v>120000</v>
       </c>
       <c r="F32" s="2">
-        <v>8500</v>
+        <v>7000</v>
       </c>
       <c r="G32"/>
     </row>
-    <row r="33" spans="3:7">
+    <row r="33" ht="14" spans="3:7">
       <c r="C33" s="2">
         <v>28</v>
       </c>
@@ -1583,11 +1583,11 @@
         <v>130000</v>
       </c>
       <c r="F33" s="2">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="G33"/>
     </row>
-    <row r="34" spans="3:7">
+    <row r="34" ht="14" spans="3:7">
       <c r="C34" s="2">
         <v>29</v>
       </c>
@@ -1596,12 +1596,88 @@
         <v>130001</v>
       </c>
       <c r="E34" s="2">
-        <v>140000</v>
+        <v>160000</v>
       </c>
       <c r="F34" s="2">
-        <v>11500</v>
+        <v>8500</v>
       </c>
       <c r="G34"/>
+    </row>
+    <row r="35" ht="14" spans="3:7">
+      <c r="C35" s="2">
+        <v>30</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="0"/>
+        <v>160001</v>
+      </c>
+      <c r="E35" s="2">
+        <v>200000</v>
+      </c>
+      <c r="F35" s="2">
+        <v>9000</v>
+      </c>
+      <c r="G35"/>
+    </row>
+    <row r="36" spans="3:6">
+      <c r="C36" s="2">
+        <v>31</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="0"/>
+        <v>200001</v>
+      </c>
+      <c r="E36" s="2">
+        <v>300000</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6">
+      <c r="C37" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="0"/>
+        <v>300001</v>
+      </c>
+      <c r="E37" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F37" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6">
+      <c r="C38" s="2">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="0"/>
+        <v>500001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F38" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
+      <c r="C39" s="2">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="0"/>
+        <v>1000001</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F39" s="2">
+        <v>20000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
   <si>
     <t>Id</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Fee</t>
+  </si>
+  <si>
+    <t>RiseFee</t>
   </si>
   <si>
     <t>int</t>
@@ -1001,35 +1004,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XER39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:XER26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="10.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.3333333333333" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:6">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1044,8 +1050,11 @@
       <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:6">
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1060,24 +1069,30 @@
       <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:6">
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="14" spans="1:16372">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1087,34 +1102,42 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H6"/>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" ht="14" spans="1:16372">
+    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D39" si="0">E6+1</f>
-        <v>101</v>
+        <f t="shared" ref="D7:D11" si="0">E6+1</f>
+        <v>11</v>
       </c>
       <c r="E7" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>200</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H7"/>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" ht="14" spans="1:16372">
+    <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1122,18 +1145,22 @@
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>300</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="H8"/>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" ht="14" spans="1:16372">
+    <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1141,18 +1168,22 @@
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>501</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>400</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H9"/>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" ht="14" spans="1:16372">
+    <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1160,18 +1191,22 @@
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>1001</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>500</v>
-      </c>
+        <v>100000000</v>
+      </c>
+      <c r="G10" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="H10"/>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" ht="14" spans="1:16372">
+    <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1179,505 +1214,184 @@
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>2001</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2">
-        <v>5000</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>600</v>
+        <v>1000000000</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1000000000</v>
       </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" ht="14" spans="1:16372">
+    <row r="12" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>5001</v>
-      </c>
-      <c r="E12" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F12" s="2">
-        <v>700</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" ht="14" spans="1:16372">
+    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>10001</v>
-      </c>
-      <c r="E13" s="2">
-        <v>15000</v>
-      </c>
-      <c r="F13" s="2">
-        <v>800</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" ht="14" spans="1:16372">
+    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>15001</v>
-      </c>
-      <c r="E14" s="2">
-        <v>20000</v>
-      </c>
-      <c r="F14" s="2">
-        <v>900</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" ht="14" spans="1:16372">
+    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>20001</v>
-      </c>
-      <c r="E15" s="2">
-        <v>25000</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1000</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" ht="14" spans="1:16372">
+    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>25001</v>
-      </c>
-      <c r="E16" s="2">
-        <v>30000</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1200</v>
-      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" ht="14" spans="1:16372">
+    <row r="17" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2">
-        <f t="shared" si="0"/>
-        <v>30001</v>
-      </c>
-      <c r="E17" s="2">
-        <v>35000</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1400</v>
-      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" ht="14" spans="1:16372">
+    <row r="18" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>35001</v>
-      </c>
-      <c r="E18" s="2">
-        <v>40000</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1600</v>
-      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" ht="14" spans="1:16372">
+    <row r="19" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>40001</v>
-      </c>
-      <c r="E19" s="2">
-        <v>45000</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1800</v>
-      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" ht="14" spans="1:16372">
+    <row r="20" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>45001</v>
-      </c>
-      <c r="E20" s="2">
-        <v>50000</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2000</v>
-      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" ht="14" spans="1:16372">
+    <row r="21" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2">
-        <v>16</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="0"/>
-        <v>50001</v>
-      </c>
-      <c r="E21" s="2">
-        <v>55000</v>
-      </c>
-      <c r="F21" s="2">
-        <v>2200</v>
-      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" ht="14" spans="1:16372">
+    <row r="22" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>55001</v>
-      </c>
-      <c r="E22" s="2">
-        <v>60000</v>
-      </c>
-      <c r="F22" s="2">
-        <v>2400</v>
-      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" ht="14" spans="1:16372">
+    <row r="23" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>60001</v>
-      </c>
-      <c r="E23" s="2">
-        <v>65000</v>
-      </c>
-      <c r="F23" s="2">
-        <v>2600</v>
-      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" ht="14" spans="1:16372">
+    <row r="24" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>65001</v>
-      </c>
-      <c r="E24" s="2">
-        <v>70000</v>
-      </c>
-      <c r="F24" s="2">
-        <v>3000</v>
-      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" ht="14" spans="1:16372">
+    <row r="25" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2">
-        <v>20</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" si="0"/>
-        <v>70001</v>
-      </c>
-      <c r="E25" s="2">
-        <v>75000</v>
-      </c>
-      <c r="F25" s="2">
-        <v>3500</v>
-      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" ht="14" spans="1:16372">
+    <row r="26" customFormat="1" customHeight="1" spans="1:7 16371:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2">
-        <v>21</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="0"/>
-        <v>75001</v>
-      </c>
-      <c r="E26" s="2">
-        <v>80000</v>
-      </c>
-      <c r="F26" s="2">
-        <v>4000</v>
-      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
       <c r="XEQ26" s="2"/>
       <c r="XER26" s="2"/>
-    </row>
-    <row r="27" ht="14" spans="3:7">
-      <c r="C27" s="2">
-        <v>22</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="0"/>
-        <v>80001</v>
-      </c>
-      <c r="E27" s="2">
-        <v>85000</v>
-      </c>
-      <c r="F27" s="2">
-        <v>4500</v>
-      </c>
-      <c r="G27"/>
-    </row>
-    <row r="28" ht="14" spans="3:7">
-      <c r="C28" s="2">
-        <v>23</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="0"/>
-        <v>85001</v>
-      </c>
-      <c r="E28" s="2">
-        <v>90000</v>
-      </c>
-      <c r="F28" s="2">
-        <v>5000</v>
-      </c>
-      <c r="G28"/>
-    </row>
-    <row r="29" ht="14" spans="3:7">
-      <c r="C29" s="2">
-        <v>24</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="0"/>
-        <v>90001</v>
-      </c>
-      <c r="E29" s="2">
-        <v>95000</v>
-      </c>
-      <c r="F29" s="2">
-        <v>5500</v>
-      </c>
-      <c r="G29"/>
-    </row>
-    <row r="30" ht="14" spans="3:7">
-      <c r="C30" s="2">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="0"/>
-        <v>95001</v>
-      </c>
-      <c r="E30" s="2">
-        <v>100000</v>
-      </c>
-      <c r="F30" s="2">
-        <v>6000</v>
-      </c>
-      <c r="G30"/>
-    </row>
-    <row r="31" ht="14" spans="3:7">
-      <c r="C31" s="2">
-        <v>26</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="0"/>
-        <v>100001</v>
-      </c>
-      <c r="E31" s="2">
-        <v>110000</v>
-      </c>
-      <c r="F31" s="2">
-        <v>6500</v>
-      </c>
-      <c r="G31"/>
-    </row>
-    <row r="32" ht="14" spans="3:7">
-      <c r="C32" s="2">
-        <v>27</v>
-      </c>
-      <c r="D32" s="2">
-        <f t="shared" si="0"/>
-        <v>110001</v>
-      </c>
-      <c r="E32" s="2">
-        <v>120000</v>
-      </c>
-      <c r="F32" s="2">
-        <v>7000</v>
-      </c>
-      <c r="G32"/>
-    </row>
-    <row r="33" ht="14" spans="3:7">
-      <c r="C33" s="2">
-        <v>28</v>
-      </c>
-      <c r="D33" s="2">
-        <f t="shared" si="0"/>
-        <v>120001</v>
-      </c>
-      <c r="E33" s="2">
-        <v>130000</v>
-      </c>
-      <c r="F33" s="2">
-        <v>7500</v>
-      </c>
-      <c r="G33"/>
-    </row>
-    <row r="34" ht="14" spans="3:7">
-      <c r="C34" s="2">
-        <v>29</v>
-      </c>
-      <c r="D34" s="2">
-        <f t="shared" si="0"/>
-        <v>130001</v>
-      </c>
-      <c r="E34" s="2">
-        <v>160000</v>
-      </c>
-      <c r="F34" s="2">
-        <v>8500</v>
-      </c>
-      <c r="G34"/>
-    </row>
-    <row r="35" ht="14" spans="3:7">
-      <c r="C35" s="2">
-        <v>30</v>
-      </c>
-      <c r="D35" s="2">
-        <f t="shared" si="0"/>
-        <v>160001</v>
-      </c>
-      <c r="E35" s="2">
-        <v>200000</v>
-      </c>
-      <c r="F35" s="2">
-        <v>9000</v>
-      </c>
-      <c r="G35"/>
-    </row>
-    <row r="36" spans="3:6">
-      <c r="C36" s="2">
-        <v>31</v>
-      </c>
-      <c r="D36" s="2">
-        <f t="shared" si="0"/>
-        <v>200001</v>
-      </c>
-      <c r="E36" s="2">
-        <v>300000</v>
-      </c>
-      <c r="F36" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="37" spans="3:6">
-      <c r="C37" s="2">
-        <v>32</v>
-      </c>
-      <c r="D37" s="2">
-        <f t="shared" si="0"/>
-        <v>300001</v>
-      </c>
-      <c r="E37" s="2">
-        <v>500000</v>
-      </c>
-      <c r="F37" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="38" spans="3:6">
-      <c r="C38" s="2">
-        <v>33</v>
-      </c>
-      <c r="D38" s="2">
-        <f t="shared" si="0"/>
-        <v>500001</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F38" s="2">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="39" spans="3:6">
-      <c r="C39" s="2">
-        <v>34</v>
-      </c>
-      <c r="D39" s="2">
-        <f t="shared" si="0"/>
-        <v>1000001</v>
-      </c>
-      <c r="E39" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="F39" s="2">
-        <v>20000</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>Id</t>
   </si>
@@ -38,10 +38,16 @@
     <t>EndLevel</t>
   </si>
   <si>
-    <t>Fee</t>
+    <t>Fee1</t>
   </si>
   <si>
-    <t>RiseFee</t>
+    <t>RiseFee1</t>
+  </si>
+  <si>
+    <t>Fee2</t>
+  </si>
+  <si>
+    <t>RiseFee2</t>
   </si>
   <si>
     <t>int</t>
@@ -1012,12 +1018,11 @@
     <col min="3" max="3" width="6.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="10.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.3333333333333" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="6" max="9" width="10.5" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1025,8 +1030,10 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1034,8 +1041,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1053,8 +1062,14 @@
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1072,27 +1087,39 @@
       <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+        <v>8</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1110,11 +1137,16 @@
       <c r="G6" s="2">
         <v>10000</v>
       </c>
-      <c r="H6"/>
+      <c r="H6" s="2">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
@@ -1133,11 +1165,16 @@
       <c r="G7" s="2">
         <v>100000</v>
       </c>
-      <c r="H7"/>
+      <c r="H7" s="2">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>100</v>
+      </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1156,11 +1193,16 @@
       <c r="G8" s="2">
         <v>1000000</v>
       </c>
-      <c r="H8"/>
+      <c r="H8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1000</v>
+      </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1179,11 +1221,16 @@
       <c r="G9" s="2">
         <v>10000000</v>
       </c>
-      <c r="H9"/>
+      <c r="H9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10000</v>
+      </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1202,11 +1249,16 @@
       <c r="G10" s="2">
         <v>100000000</v>
       </c>
-      <c r="H10"/>
+      <c r="H10" s="2">
+        <v>100000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>100000</v>
+      </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1225,10 +1277,16 @@
       <c r="G11" s="2">
         <v>1000000000</v>
       </c>
+      <c r="H11" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1000000</v>
+      </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="12" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1236,10 +1294,12 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1247,10 +1307,12 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1258,10 +1320,12 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1269,10 +1333,12 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1280,10 +1346,12 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="17" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1291,10 +1359,12 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="18" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1302,10 +1372,12 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="19" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1313,10 +1385,12 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="20" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1324,10 +1398,12 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" ht="18" customHeight="1" spans="1:7 16371:16372">
+    <row r="21" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1335,10 +1411,12 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="22" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1346,10 +1424,12 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="23" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1357,10 +1437,12 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="24" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1368,10 +1450,12 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="25" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1379,10 +1463,12 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:7 16371:16372">
+    <row r="26" customFormat="1" customHeight="1" spans="1:9 16371:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1390,6 +1476,8 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
       <c r="XEQ26" s="2"/>
       <c r="XER26" s="2"/>
     </row>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1160,13 +1160,13 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G7" s="2">
         <v>100000</v>
       </c>
       <c r="H7" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
@@ -1188,13 +1188,13 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="G8" s="2">
         <v>1000000</v>
       </c>
       <c r="H8" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I8" s="2">
         <v>1000</v>
@@ -1216,13 +1216,13 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
       <c r="G9" s="2">
         <v>10000000</v>
       </c>
       <c r="H9" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="I9" s="2">
         <v>10000</v>
@@ -1244,13 +1244,13 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="G10" s="2">
         <v>100000000</v>
       </c>
       <c r="H10" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I10" s="2">
         <v>100000</v>
@@ -1272,13 +1272,13 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>1000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="G11" s="2">
         <v>1000000000</v>
       </c>
       <c r="H11" s="2">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="I11" s="2">
         <v>1000000</v>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1018,7 +1018,9 @@
     <col min="3" max="3" width="6.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.125" style="2" customWidth="1"/>
-    <col min="6" max="9" width="10.5" style="2" customWidth="1"/>
+    <col min="6" max="7" width="10.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1132,16 +1134,16 @@
         <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="G6" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
@@ -1160,16 +1162,16 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="G7" s="2">
         <v>200000</v>
       </c>
-      <c r="G7" s="2">
-        <v>100000</v>
-      </c>
       <c r="H7" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I7" s="2">
         <v>200</v>
-      </c>
-      <c r="I7" s="2">
-        <v>100</v>
       </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
@@ -1188,16 +1190,16 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>2000000</v>
+        <v>3300000</v>
       </c>
       <c r="G8" s="2">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="H8" s="2">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="I8" s="2">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
@@ -1216,16 +1218,16 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>20000000</v>
+        <v>6400000</v>
       </c>
       <c r="G9" s="2">
-        <v>10000000</v>
+        <v>400000</v>
       </c>
       <c r="H9" s="2">
-        <v>20000</v>
+        <v>6400</v>
       </c>
       <c r="I9" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
@@ -1244,16 +1246,16 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>200000000</v>
+        <v>10000000</v>
       </c>
       <c r="G10" s="2">
-        <v>100000000</v>
+        <v>1000000</v>
       </c>
       <c r="H10" s="2">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="I10" s="2">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
@@ -1272,16 +1274,16 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>2000000000</v>
+        <v>20000000</v>
       </c>
       <c r="G11" s="2">
-        <v>1000000000</v>
+        <v>2000000</v>
       </c>
       <c r="H11" s="2">
-        <v>2000000</v>
+        <v>20000</v>
       </c>
       <c r="I11" s="2">
-        <v>1000000</v>
+        <v>2000</v>
       </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1205,8 +1205,6 @@
       <c r="XER8" s="2"/>
     </row>
     <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
       <c r="C9" s="2">
         <v>4</v>
       </c>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1137,13 +1137,13 @@
         <v>100000</v>
       </c>
       <c r="G6" s="2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
       </c>
       <c r="I6" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
@@ -1162,16 +1162,18 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>1200000</v>
+        <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6</f>
+        <v>550000</v>
       </c>
       <c r="G7" s="2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="H7" s="2">
-        <v>1200</v>
+        <f t="shared" ref="H7:H11" si="2">H6+(E6-D6)*I6</f>
+        <v>550</v>
       </c>
       <c r="I7" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
@@ -1190,16 +1192,18 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>3300000</v>
+        <f t="shared" si="1"/>
+        <v>1450000</v>
       </c>
       <c r="G8" s="2">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="H8" s="2">
-        <v>3300</v>
+        <f t="shared" si="2"/>
+        <v>1450</v>
       </c>
       <c r="I8" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
@@ -1216,16 +1220,18 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>6400000</v>
+        <f t="shared" si="1"/>
+        <v>3250000</v>
       </c>
       <c r="G9" s="2">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="2">
-        <v>6400</v>
+        <f t="shared" si="2"/>
+        <v>2800</v>
       </c>
       <c r="I9" s="2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
@@ -1244,16 +1250,18 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>10000000</v>
+        <f t="shared" si="1"/>
+        <v>5950000</v>
       </c>
       <c r="G10" s="2">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="H10" s="2">
-        <v>10000</v>
+        <f t="shared" si="2"/>
+        <v>4600</v>
       </c>
       <c r="I10" s="2">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
@@ -1272,16 +1280,18 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>20000000</v>
+        <f t="shared" si="1"/>
+        <v>9550000</v>
       </c>
       <c r="G11" s="2">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="H11" s="2">
-        <v>20000</v>
+        <f t="shared" si="2"/>
+        <v>7300</v>
       </c>
       <c r="I11" s="2">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="10">
   <si>
     <t>Id</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1209,6 +1212,12 @@
       <c r="XER8" s="2"/>
     </row>
     <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1237,8 +1246,12 @@
       <c r="XER9" s="2"/>
     </row>
     <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1267,8 +1280,12 @@
       <c r="XER10" s="2"/>
     </row>
     <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C11" s="2">
         <v>6</v>
       </c>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
   <si>
     <t>Id</t>
   </si>
@@ -1212,12 +1212,6 @@
       <c r="XER8" s="2"/>
     </row>
     <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1140,7 +1140,7 @@
         <v>100000</v>
       </c>
       <c r="G6" s="2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
@@ -1165,15 +1165,15 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6</f>
-        <v>550000</v>
+        <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
+        <v>1200000</v>
       </c>
       <c r="G7" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" ref="H7:H11" si="2">H6+(E6-D6)*I6</f>
-        <v>550</v>
+        <f t="shared" ref="H7:H11" si="2">H6+(E6-D6)*I6+I7</f>
+        <v>650</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>1450000</v>
+        <v>3300000</v>
       </c>
       <c r="G8" s="2">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>1450</v>
+        <v>1700</v>
       </c>
       <c r="I8" s="2">
         <v>150</v>
@@ -1224,14 +1224,14 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>3250000</v>
+        <v>6400000</v>
       </c>
       <c r="G9" s="2">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>3250</v>
       </c>
       <c r="I9" s="2">
         <v>200</v>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>5950000</v>
+        <v>10600000</v>
       </c>
       <c r="G10" s="2">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>4600</v>
+        <v>5350</v>
       </c>
       <c r="I10" s="2">
         <v>300</v>
@@ -1292,14 +1292,14 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="1"/>
-        <v>9550000</v>
+        <v>16800000</v>
       </c>
       <c r="G11" s="2">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>7300</v>
+        <v>8550</v>
       </c>
       <c r="I11" s="2">
         <v>500</v>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>Id</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>long</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1196,10 +1193,10 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>3300000</v>
+        <v>3400000</v>
       </c>
       <c r="G8" s="2">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
@@ -1224,10 +1221,10 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>6400000</v>
+        <v>7700000</v>
       </c>
       <c r="G9" s="2">
-        <v>400000</v>
+        <v>700000</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
@@ -1240,12 +1237,8 @@
       <c r="XER9" s="2"/>
     </row>
     <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1258,10 +1251,10 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>10600000</v>
+        <v>15000000</v>
       </c>
       <c r="G10" s="2">
-        <v>600000</v>
+        <v>1000000</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
@@ -1274,12 +1267,8 @@
       <c r="XER10" s="2"/>
     </row>
     <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1292,10 +1281,10 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="1"/>
-        <v>16800000</v>
+        <v>25500000</v>
       </c>
       <c r="G11" s="2">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>

--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -41,13 +41,13 @@
     <t>Fee1</t>
   </si>
   <si>
-    <t>RiseFee1</t>
+    <t>RiseType1</t>
   </si>
   <si>
     <t>Fee2</t>
   </si>
   <si>
-    <t>RiseFee2</t>
+    <t>RiseType2</t>
   </si>
   <si>
     <t>int</t>
@@ -686,11 +686,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1010,21 +1013,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XER26"/>
+  <dimension ref="A1:XEQ26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12" style="2" customWidth="1"/>
     <col min="6" max="7" width="10.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.5833333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1035,7 +1038,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1046,7 +1049,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1071,7 +1074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1096,7 +1099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1111,17 +1114,17 @@
       <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
+      <c r="G5" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+      <c r="I5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1131,172 +1134,102 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2">
         <v>100000</v>
       </c>
       <c r="G6" s="2">
-        <v>100000</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I6" s="2">
-        <v>50</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="XEP6" s="2"/>
       <c r="XEQ6" s="2"/>
-      <c r="XER6" s="2"/>
-    </row>
-    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D11" si="0">E6+1</f>
-        <v>11</v>
+        <f>E6+1</f>
+        <v>31</v>
       </c>
       <c r="E7" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
-        <v>1200000</v>
+        <v>120000</v>
       </c>
       <c r="G7" s="2">
-        <v>200000</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" ref="H7:H11" si="2">H6+(E6-D6)*I6+I7</f>
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="I7" s="2">
-        <v>100</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="XEP7" s="2"/>
       <c r="XEQ7" s="2"/>
-      <c r="XER7" s="2"/>
-    </row>
-    <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="E8" s="2">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
-        <v>3400000</v>
-      </c>
-      <c r="G8" s="2">
-        <v>400000</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="2"/>
-        <v>1700</v>
-      </c>
-      <c r="I8" s="2">
-        <v>150</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="XEP8" s="2"/>
       <c r="XEQ8" s="2"/>
-      <c r="XER8" s="2"/>
-    </row>
-    <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="E9" s="2">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="1"/>
-        <v>7700000</v>
-      </c>
-      <c r="G9" s="2">
-        <v>700000</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="2"/>
-        <v>3250</v>
-      </c>
-      <c r="I9" s="2">
-        <v>200</v>
-      </c>
+    </row>
+    <row r="9" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="XEP9" s="2"/>
       <c r="XEQ9" s="2"/>
-      <c r="XER9" s="2"/>
-    </row>
-    <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="10" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="E10" s="2">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>15000000</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="2"/>
-        <v>5350</v>
-      </c>
-      <c r="I10" s="2">
-        <v>300</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="XEP10" s="2"/>
       <c r="XEQ10" s="2"/>
-      <c r="XER10" s="2"/>
-    </row>
-    <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="11" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="E11" s="2">
-        <v>60</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>25500000</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="2"/>
-        <v>8550</v>
-      </c>
-      <c r="I11" s="2">
-        <v>500</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="XEP11" s="2"/>
       <c r="XEQ11" s="2"/>
-      <c r="XER11" s="2"/>
-    </row>
-    <row r="12" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="12" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1306,10 +1239,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
+      <c r="XEP12" s="2"/>
       <c r="XEQ12" s="2"/>
-      <c r="XER12" s="2"/>
-    </row>
-    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1319,10 +1252,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
+      <c r="XEP13" s="2"/>
       <c r="XEQ13" s="2"/>
-      <c r="XER13" s="2"/>
-    </row>
-    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1332,10 +1265,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
+      <c r="XEP14" s="2"/>
       <c r="XEQ14" s="2"/>
-      <c r="XER14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1345,10 +1278,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
+      <c r="XEP15" s="2"/>
       <c r="XEQ15" s="2"/>
-      <c r="XER15" s="2"/>
-    </row>
-    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1358,10 +1291,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
+      <c r="XEP16" s="2"/>
       <c r="XEQ16" s="2"/>
-      <c r="XER16" s="2"/>
-    </row>
-    <row r="17" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="17" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1371,10 +1304,10 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
+      <c r="XEP17" s="2"/>
       <c r="XEQ17" s="2"/>
-      <c r="XER17" s="2"/>
-    </row>
-    <row r="18" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="18" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1384,10 +1317,10 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
+      <c r="XEP18" s="2"/>
       <c r="XEQ18" s="2"/>
-      <c r="XER18" s="2"/>
-    </row>
-    <row r="19" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="19" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1397,10 +1330,10 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="XEP19" s="2"/>
       <c r="XEQ19" s="2"/>
-      <c r="XER19" s="2"/>
-    </row>
-    <row r="20" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="20" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1410,10 +1343,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
+      <c r="XEP20" s="2"/>
       <c r="XEQ20" s="2"/>
-      <c r="XER20" s="2"/>
-    </row>
-    <row r="21" customFormat="1" ht="18" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="21" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1423,10 +1356,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
+      <c r="XEP21" s="2"/>
       <c r="XEQ21" s="2"/>
-      <c r="XER21" s="2"/>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1436,10 +1369,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
+      <c r="XEP22" s="2"/>
       <c r="XEQ22" s="2"/>
-      <c r="XER22" s="2"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1449,10 +1382,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
+      <c r="XEP23" s="2"/>
       <c r="XEQ23" s="2"/>
-      <c r="XER23" s="2"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1462,10 +1395,10 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
+      <c r="XEP24" s="2"/>
       <c r="XEQ24" s="2"/>
-      <c r="XER24" s="2"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1475,10 +1408,10 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
+      <c r="XEP25" s="2"/>
       <c r="XEQ25" s="2"/>
-      <c r="XER25" s="2"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:9 16371:16372">
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="1:9 16370:16371">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1488,8 +1421,8 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
+      <c r="XEP26" s="2"/>
       <c r="XEQ26" s="2"/>
-      <c r="XER26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
